--- a/Dataset_Dmart_Cleaning_Structuring .xlsx
+++ b/Dataset_Dmart_Cleaning_Structuring .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4eace367ba376db1/Desktop/advance excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6BA3354-E551-4B11-9691-6A5E7D566559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{C638EB09-CBA5-4505-941A-35BC28B6F476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DA77C55-5D9A-4B53-B466-A9C4C07F5C1F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="Sheet2" sheetId="6" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="7" r:id="rId3"/>
     <sheet name="Sheet4" sheetId="8" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="9" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet3!$L$19:$L$26</definedName>
@@ -37,7 +38,7 @@
       </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="gT5L9Uh5Mkce+NjaHPxVAbIJlDW9RbqkjfO6mNdsl18="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="gT5L9Uh5Mkce+NjaHPxVAbIJlDW9RbqkjfO6mNdsl18="/>
     </ext>
   </extLst>
 </workbook>
@@ -66,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4203" uniqueCount="691">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4229" uniqueCount="706">
   <si>
     <t>Column1</t>
   </si>
@@ -2139,6 +2140,65 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>bonus amount</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">EMP </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ID</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">EmployeeID </t>
+  </si>
+  <si>
+    <t>JAN</t>
+  </si>
+  <si>
+    <t>FEB</t>
+  </si>
+  <si>
+    <t>MARCH</t>
+  </si>
+  <si>
+    <t>APRIL</t>
+  </si>
+  <si>
+    <t>MAY</t>
+  </si>
+  <si>
+    <t>COST</t>
+  </si>
+  <si>
+    <t>TRAVEL</t>
+  </si>
+  <si>
+    <t>SALES</t>
+  </si>
+  <si>
+    <t>PROFIT</t>
+  </si>
+  <si>
+    <t>MONTH</t>
+  </si>
+  <si>
+    <t>using vlookup</t>
+  </si>
+  <si>
+    <t>ORDER ID</t>
   </si>
 </sst>
 </file>
@@ -2149,11 +2209,18 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="&quot;₹&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2258,8 +2325,17 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2293,6 +2369,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4F4F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2453,43 +2535,43 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2498,27 +2580,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2528,63 +2610,71 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="17" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -3620,12 +3710,12 @@
         <v>NO</v>
       </c>
       <c r="Q4" s="1"/>
-      <c r="R4" s="59" t="s">
+      <c r="R4" s="63" t="s">
         <v>646</v>
       </c>
-      <c r="S4" s="59"/>
-      <c r="T4" s="59"/>
-      <c r="U4" s="59"/>
+      <c r="S4" s="63"/>
+      <c r="T4" s="63"/>
+      <c r="U4" s="63"/>
       <c r="V4" s="47">
         <f>SUMIF(Table2[payment_mode],"=UPI",Table2[sales])</f>
         <v>386412.25</v>
@@ -3688,12 +3778,12 @@
         <v>YES</v>
       </c>
       <c r="Q5" s="1"/>
-      <c r="R5" s="60" t="s">
+      <c r="R5" s="64" t="s">
         <v>647</v>
       </c>
-      <c r="S5" s="61"/>
-      <c r="T5" s="61"/>
-      <c r="U5" s="62"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="66"/>
       <c r="V5" s="47">
         <f>SUMIF(Table2[payment_mode],"=CARD",Table2[sales])</f>
         <v>413292.63999999996</v>
@@ -3756,12 +3846,12 @@
         <v>NO</v>
       </c>
       <c r="Q6" s="1"/>
-      <c r="R6" s="60" t="s">
+      <c r="R6" s="64" t="s">
         <v>648</v>
       </c>
-      <c r="S6" s="61"/>
-      <c r="T6" s="61"/>
-      <c r="U6" s="62"/>
+      <c r="S6" s="65"/>
+      <c r="T6" s="65"/>
+      <c r="U6" s="66"/>
       <c r="V6" s="47">
         <f>SUMIF(Table2[payment_mode],"=CASH",Table2[sales])</f>
         <v>522964.3</v>
@@ -3950,13 +4040,13 @@
         <v>NO</v>
       </c>
       <c r="Q9" s="1"/>
-      <c r="R9" s="63" t="s">
+      <c r="R9" s="67" t="s">
         <v>661</v>
       </c>
-      <c r="S9" s="63"/>
-      <c r="T9" s="63"/>
-      <c r="U9" s="63"/>
-      <c r="V9" s="63"/>
+      <c r="S9" s="67"/>
+      <c r="T9" s="67"/>
+      <c r="U9" s="67"/>
+      <c r="V9" s="67"/>
       <c r="W9" s="46" cm="1">
         <f t="array" ref="W9">SUMIFS(SALES,Category,"Clothing",Region,"East")</f>
         <v>60655.859999999993</v>
@@ -4018,13 +4108,13 @@
         <v>NO</v>
       </c>
       <c r="Q10" s="1"/>
-      <c r="R10" s="63" t="s">
+      <c r="R10" s="67" t="s">
         <v>662</v>
       </c>
-      <c r="S10" s="63"/>
-      <c r="T10" s="63"/>
-      <c r="U10" s="63"/>
-      <c r="V10" s="63"/>
+      <c r="S10" s="67"/>
+      <c r="T10" s="67"/>
+      <c r="U10" s="67"/>
+      <c r="V10" s="67"/>
       <c r="W10" s="46" cm="1">
         <f t="array" ref="W10">SUMIFS(SALES,Category,"Electronics",Region,"North",discount,"&gt;40%")</f>
         <v>36091.269999999997</v>
@@ -6342,8 +6432,12 @@
         <v>NO</v>
       </c>
       <c r="Q45" s="1"/>
-      <c r="R45" s="1"/>
-      <c r="S45" s="1"/>
+      <c r="R45" s="56" t="s">
+        <v>705</v>
+      </c>
+      <c r="S45" s="56" t="s">
+        <v>701</v>
+      </c>
       <c r="T45" s="1"/>
       <c r="U45" s="1"/>
       <c r="V45" s="1"/>
@@ -6405,8 +6499,13 @@
         <v>NO</v>
       </c>
       <c r="Q46" s="1"/>
-      <c r="R46" s="1"/>
-      <c r="S46" s="1"/>
+      <c r="R46" s="56" t="s">
+        <v>72</v>
+      </c>
+      <c r="S46" s="56">
+        <f>VLOOKUP(R46,Table2[],MATCH(S45,Table2[#Headers],0),FALSE)</f>
+        <v>4754.72</v>
+      </c>
       <c r="T46" s="1"/>
       <c r="U46" s="1"/>
       <c r="V46" s="1"/>
@@ -48492,7 +48591,7 @@
     <mergeCell ref="R9:V9"/>
     <mergeCell ref="R10:V10"/>
   </mergeCells>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="G2">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="clothing">
       <formula>NOT(ISERROR(SEARCH("clothing",G2)))</formula>
@@ -48528,6 +48627,11 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R46" xr:uid="{7D98847F-57ED-439A-89D3-CEDADF8B9570}">
+      <formula1>$A$2:$A$499</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
@@ -49257,7 +49361,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16CFF2D3-E603-41C0-A769-745F21BD7E78}">
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
@@ -49265,6 +49369,8 @@
     <col min="3" max="3" width="13.21875" customWidth="1"/>
     <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.77734375" customWidth="1"/>
+    <col min="10" max="10" width="16.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -49425,7 +49531,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E17">
         <v>70000</v>
       </c>
@@ -49433,7 +49539,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E18">
         <v>50000</v>
       </c>
@@ -49441,7 +49547,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E19" t="s">
         <v>636</v>
       </c>
@@ -49449,7 +49555,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>640</v>
       </c>
@@ -49460,7 +49566,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>27</v>
       </c>
@@ -49468,7 +49574,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>45</v>
       </c>
@@ -49476,7 +49582,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>65</v>
       </c>
@@ -49484,7 +49590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>60</v>
       </c>
@@ -49492,7 +49598,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>36</v>
       </c>
@@ -49500,89 +49606,166 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="34" t="s">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="34"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="F28" s="34" t="s">
+        <v>692</v>
+      </c>
+      <c r="G28" s="37" t="s">
         <v>605</v>
       </c>
-      <c r="B28" s="37" t="s">
+      <c r="H28" s="37" t="s">
         <v>633</v>
       </c>
-      <c r="C28" s="37" t="s">
+      <c r="I28" s="37" t="s">
         <v>635</v>
       </c>
-      <c r="D28" s="37" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="42" t="s">
+      <c r="J28" s="61" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="42"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="59"/>
+      <c r="D29" s="39"/>
+      <c r="F29" s="42">
+        <v>1001</v>
+      </c>
+      <c r="G29" s="60" t="s">
         <v>610</v>
       </c>
-      <c r="B29" s="39">
+      <c r="H29" s="39">
         <v>70000</v>
       </c>
-      <c r="C29" s="39"/>
-      <c r="D29" s="39"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="42" t="s">
+      <c r="I29" s="59">
+        <v>0.1</v>
+      </c>
+      <c r="J29" s="39">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="42"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="59"/>
+      <c r="D30" s="39"/>
+      <c r="F30" s="42">
+        <v>1002</v>
+      </c>
+      <c r="G30" s="60" t="s">
         <v>612</v>
       </c>
-      <c r="B30" s="39">
-        <v>50000</v>
-      </c>
-      <c r="C30" s="39"/>
-      <c r="D30" s="39"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="42" t="s">
+      <c r="H30" s="39">
+        <v>54000</v>
+      </c>
+      <c r="I30" s="59">
+        <v>0.05</v>
+      </c>
+      <c r="J30" s="39">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" s="42"/>
+      <c r="B31" s="39"/>
+      <c r="C31" s="59"/>
+      <c r="D31" s="39"/>
+      <c r="F31" s="42">
+        <v>1003</v>
+      </c>
+      <c r="G31" s="60" t="s">
         <v>614</v>
       </c>
-      <c r="B31" s="39">
+      <c r="H31" s="39">
         <v>45000</v>
       </c>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="42" t="s">
+      <c r="I31" s="59">
+        <v>0</v>
+      </c>
+      <c r="J31" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" s="42"/>
+      <c r="B32" s="39"/>
+      <c r="C32" s="59"/>
+      <c r="D32" s="39"/>
+      <c r="F32" s="42">
+        <v>1004</v>
+      </c>
+      <c r="G32" s="60" t="s">
         <v>616</v>
       </c>
-      <c r="B32" s="39">
+      <c r="H32" s="39">
         <v>75000</v>
       </c>
-      <c r="C32" s="39"/>
-      <c r="D32" s="39"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="43" t="s">
+      <c r="I32" s="59">
+        <v>0.15</v>
+      </c>
+      <c r="J32" s="39">
+        <v>11250</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" s="43"/>
+      <c r="B33" s="39"/>
+      <c r="C33" s="59"/>
+      <c r="D33" s="39"/>
+      <c r="F33" s="43">
+        <v>1005</v>
+      </c>
+      <c r="G33" s="60" t="s">
         <v>634</v>
       </c>
-      <c r="B33" s="39">
+      <c r="H33" s="39">
         <v>55000</v>
       </c>
-      <c r="C33" s="39"/>
-      <c r="D33" s="39"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="64" t="s">
+      <c r="I33" s="59">
+        <v>0.05</v>
+      </c>
+      <c r="J33" s="39">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="F35" s="62" t="s">
+        <v>693</v>
+      </c>
+      <c r="G35" s="62" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" s="68" t="s">
         <v>645</v>
       </c>
-      <c r="B36" s="64"/>
+      <c r="B36" s="68"/>
       <c r="C36" s="45">
         <f>SUMIF(B29:B33,"&gt;50000",B29:B33)</f>
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="40" spans="1:6" ht="19.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="41" spans="1:6" ht="16.8" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="42" spans="1:6" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="F36" s="60">
+        <v>1001</v>
+      </c>
+      <c r="G36" s="33">
+        <f>VLOOKUP(F36,F28:J33,3,FALSE)</f>
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="40" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="41" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="42" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E42" s="54"/>
       <c r="F42" s="55"/>
     </row>
-    <row r="44" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="45" spans="1:6" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="45" spans="1:10" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="50" t="s">
         <v>2</v>
       </c>
@@ -49600,7 +49783,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="48" t="s">
         <v>650</v>
       </c>
@@ -49618,7 +49801,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="48" t="s">
         <v>650</v>
       </c>
@@ -49629,7 +49812,7 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="48"/>
       <c r="B48" s="48" t="s">
         <v>660</v>
@@ -49687,4 +49870,190 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4916EDE8-FB41-4E3A-9A95-E11D9EAF4E94}">
+  <dimension ref="A3:L14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="13.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="33"/>
+      <c r="B3" s="33" t="s">
+        <v>694</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>695</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>696</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>697</v>
+      </c>
+      <c r="F3" s="33" t="s">
+        <v>698</v>
+      </c>
+      <c r="K3" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="33" t="s">
+        <v>699</v>
+      </c>
+      <c r="B4" s="33">
+        <v>100</v>
+      </c>
+      <c r="C4" s="33">
+        <v>585</v>
+      </c>
+      <c r="D4" s="33">
+        <v>333</v>
+      </c>
+      <c r="E4" s="33">
+        <v>745</v>
+      </c>
+      <c r="F4" s="33">
+        <v>222</v>
+      </c>
+      <c r="H4" s="33" t="s">
+        <v>703</v>
+      </c>
+      <c r="I4" s="33" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="33" t="s">
+        <v>700</v>
+      </c>
+      <c r="B5" s="33">
+        <v>100</v>
+      </c>
+      <c r="C5" s="33">
+        <v>500</v>
+      </c>
+      <c r="D5" s="33">
+        <v>600</v>
+      </c>
+      <c r="E5" s="33">
+        <v>700</v>
+      </c>
+      <c r="F5" s="33">
+        <v>900</v>
+      </c>
+      <c r="H5" s="33" t="s">
+        <v>701</v>
+      </c>
+      <c r="I5" s="33">
+        <f>HLOOKUP(I4,A3:F7,4,0)</f>
+        <v>7000</v>
+      </c>
+      <c r="K5" t="s">
+        <v>703</v>
+      </c>
+      <c r="L5" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="33" t="s">
+        <v>701</v>
+      </c>
+      <c r="B6" s="33">
+        <v>2000</v>
+      </c>
+      <c r="C6" s="33">
+        <v>7000</v>
+      </c>
+      <c r="D6" s="33">
+        <v>8000</v>
+      </c>
+      <c r="E6" s="33">
+        <v>6000</v>
+      </c>
+      <c r="F6" s="33">
+        <v>4000</v>
+      </c>
+      <c r="H6" s="33" t="s">
+        <v>700</v>
+      </c>
+      <c r="I6" s="33">
+        <f>HLOOKUP(I4,A3:F7,3,0)</f>
+        <v>500</v>
+      </c>
+      <c r="K6" t="s">
+        <v>701</v>
+      </c>
+      <c r="L6">
+        <f>VLOOKUP(K6,A3:F7,6,0)</f>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="33" t="s">
+        <v>702</v>
+      </c>
+      <c r="B7" s="33">
+        <v>400</v>
+      </c>
+      <c r="C7" s="33">
+        <v>500</v>
+      </c>
+      <c r="D7" s="33">
+        <v>300</v>
+      </c>
+      <c r="E7" s="33">
+        <v>300</v>
+      </c>
+      <c r="F7" s="33">
+        <v>200</v>
+      </c>
+      <c r="H7" s="33" t="s">
+        <v>699</v>
+      </c>
+      <c r="I7" s="33">
+        <f>HLOOKUP(I4,A3:F7,2,0)</f>
+        <v>585</v>
+      </c>
+      <c r="K7" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H8" s="33" t="s">
+        <v>702</v>
+      </c>
+      <c r="I8" s="33">
+        <f>HLOOKUP(I4,A3:F7,5,0)</f>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B10" s="33"/>
+      <c r="C10" s="33"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C11" s="33"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C12" s="33"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C13" s="33"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C14" s="33"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Dataset_Dmart_Cleaning_Structuring .xlsx
+++ b/Dataset_Dmart_Cleaning_Structuring .xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4eace367ba376db1/Desktop/advance excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{C638EB09-CBA5-4505-941A-35BC28B6F476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DA77C55-5D9A-4B53-B466-A9C4C07F5C1F}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{7FB03954-5734-4D9E-8203-5A5373883308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21640A90-5FDA-4D15-89B6-AB8ADB1EC5BB}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="524" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6630,10 +6630,10 @@
         <v>YES</v>
       </c>
       <c r="Q48" s="1"/>
-      <c r="R48" s="1"/>
-      <c r="S48" s="1" t="s">
+      <c r="R48" s="1" t="s">
         <v>690</v>
       </c>
+      <c r="S48" s="1"/>
       <c r="T48" s="1"/>
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
@@ -49874,7 +49874,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4916EDE8-FB41-4E3A-9A95-E11D9EAF4E94}">
-  <dimension ref="A3:L14"/>
+  <dimension ref="A3:L8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="13.5546875" customWidth="1"/>
@@ -50033,26 +50033,6 @@
         <v>500</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="33"/>
-      <c r="C9" s="33"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="33"/>
-      <c r="C10" s="33"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C11" s="33"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C12" s="33"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C13" s="33"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C14" s="33"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
